--- a/docs/qq.xlsx
+++ b/docs/qq.xlsx
@@ -276,7 +276,7 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>95.500000</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="3">
@@ -287,7 +287,7 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>88.750000</v>
+        <v>88.75</v>
       </c>
     </row>
     <row r="4">
@@ -298,7 +298,7 @@
         <v>28</v>
       </c>
       <c r="C4">
-        <v>92.000000</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -323,7 +323,7 @@
     </row>
     <row r="3">
       <c r="C3">
-        <v>3.141590</v>
+        <v>3.14159</v>
       </c>
     </row>
   </sheetData>
